--- a/databases/tabela_resumo_clusters_ans_final2.xlsx
+++ b/databases/tabela_resumo_clusters_ans_final2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,7 +418,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>3857</v>
+        <v>4542</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -427,19 +427,19 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.49</v>
+        <v>1.02</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="3">
@@ -454,96 +454,27 @@
         </is>
       </c>
       <c r="C3">
-        <v>1335</v>
+        <v>1028</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="E3">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="F3">
-        <v>5.47</v>
+        <v>9.5</v>
       </c>
       <c r="G3">
-        <v>5.2</v>
+        <v>8.1</v>
       </c>
       <c r="H3">
-        <v>1.78</v>
+        <v>5.94</v>
       </c>
       <c r="I3">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ans_tx_abortos_mil_mulheres_valor_medio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>377</v>
-      </c>
-      <c r="D4">
-        <v>9.5</v>
-      </c>
-      <c r="E4">
-        <v>10.7</v>
-      </c>
-      <c r="F4">
-        <v>13.4</v>
-      </c>
-      <c r="G4">
-        <v>12.2</v>
-      </c>
-      <c r="H4">
-        <v>4.29</v>
-      </c>
-      <c r="I4">
-        <v>14.8</v>
-      </c>
-      <c r="J4">
-        <v>45.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ans_tx_abortos_mil_mulheres_valor_medio</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>146.3</v>
-      </c>
-      <c r="E5">
-        <v>146.3</v>
-      </c>
-      <c r="F5">
-        <v>146.3</v>
-      </c>
-      <c r="G5">
-        <v>146.3</v>
-      </c>
-      <c r="I5">
-        <v>146.3</v>
-      </c>
-      <c r="J5">
         <v>146.3</v>
       </c>
     </row>
